--- a/Config/Excel/DT_WeaponConfig.xlsx
+++ b/Config/Excel/DT_WeaponConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\UnrealDeepRock_Config_Preview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E154D340-66E0-49B1-BC9A-56D8865C729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAC76D25-7F1C-48BA-A5DF-298D9B14F3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
   <si>
     <t>#TABLE=DT_WeaponConfig</t>
   </si>
@@ -113,24 +113,187 @@
   </si>
   <si>
     <t>Ranger_ArcaneCrossbow</t>
-  </si>
-  <si>
-    <t>游侠主武器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠主武器；高频易伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>奥术连弩</t>
-  </si>
-  <si>
-    <t>Ranger_ArcaneCrossbow_RapidBolt,Ranger_ArcaneCrossbow_ChargedMissile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Ranger_ArcaneCrossbow_RapidBolt</t>
-  </si>
-  <si>
-    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bolt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Muzzle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger_SawedOffShotgun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠副武器候选；近距离爆发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单手短管霰弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger_SawedOffShotgun_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger_FullAutoPistol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠副武器候选；全距离稳定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全自动手枪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger_FullAutoPistol_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightAmmo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger_ThrowingKnife</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游侠副武器候选；高单体伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranger_ThrowingKnife_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knife</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Driller_Flamethrower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆破主武器；持续火焰与着火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰喷射器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Driller_Flamethrower_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fuel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Driller_Revolver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆破副武器候选；高精度单发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左轮手枪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Driller_Revolver_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeavyAmmo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Driller_RocketLauncher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆破副武器候选；范围爆发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火箭筒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Driller_RocketLauncher_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rocket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer_AssaultRifle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匠师主武器；稳定持续输出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突击步枪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer_AssaultRifle_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RifleAmmo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer_ChainsawLauncher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匠师副武器；直线贯穿与流血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链锯发射器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer_ChainsawLauncher_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chainsaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -477,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
@@ -610,22 +773,278 @@
         <v>33</v>
       </c>
       <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5">
+        <v>36</v>
+      </c>
+      <c r="H5">
+        <v>288</v>
+      </c>
+      <c r="I5">
+        <v>1.6</v>
+      </c>
+      <c r="K5" t="s">
         <v>35</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>24</v>
+      </c>
+      <c r="I6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>90</v>
+      </c>
+      <c r="I7">
+        <v>1.8</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>16</v>
+      </c>
+      <c r="I8">
+        <v>1.2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>400</v>
+      </c>
+      <c r="I9">
+        <v>2.5</v>
+      </c>
+      <c r="K9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>36</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>2.8</v>
+      </c>
+      <c r="K11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>180</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>20</v>
+      </c>
+      <c r="I13">
+        <v>2.4</v>
+      </c>
+      <c r="K13" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/DT_WeaponConfig.xlsx
+++ b/Config/Excel/DT_WeaponConfig.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\letsdeeprock-profession-preview\com-final-serial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAC76D25-7F1C-48BA-A5DF-298D9B14F3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74D79970-B10C-469A-8089-D6CCDEAAFBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -196,62 +196,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Driller_Flamethrower</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆破主武器；持续火焰与着火</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>火焰喷射器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Driller_Flamethrower_Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Fuel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Driller_Revolver</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆破副武器候选；高精度单发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>左轮手枪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Driller_Revolver_Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HeavyAmmo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Driller_RocketLauncher</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆破副武器候选；范围爆发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>火箭筒</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Driller_RocketLauncher_Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Rocket</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -293,6 +257,42 @@
   </si>
   <si>
     <t>Chainsaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Flamethrower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist primary; sustained fire and burning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Flamethrower_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Revolver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist secondary candidate; accurate single shot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_Revolver_Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_RocketLauncher</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist secondary candidate; area burst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolitionist_RocketLauncher_Default</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -889,22 +889,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" t="s">
         <v>52</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -921,22 +921,22 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -953,22 +953,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -985,22 +985,22 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>30</v>
@@ -1017,22 +1017,22 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>4</v>
